--- a/assets/Synthèse.xlsx
+++ b/assets/Synthèse.xlsx
@@ -1,22 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29426"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29929"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\LIN Dany\OneDrive - SCHOLA NOVA\Bureau\Apple\assets\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\LIN Dany\OneDrive - SCHOLA NOVA\Bureau\Dany-Portfolio\assets\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8F987A3B-8588-4064-89D0-9D9AD62F0F16}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{93A976A9-3338-4AB8-91B5-C35044DDE2D1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="11424" yWindow="0" windowWidth="11712" windowHeight="12336" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Tableau de synthèse Épreuve E4" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">'Tableau de synthèse Épreuve E4'!$A$1:$H$35</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">'Tableau de synthèse Épreuve E4'!$A$1:$H$32</definedName>
   </definedNames>
   <calcPr calcId="191028"/>
   <extLst>
@@ -39,24 +39,15 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="61" uniqueCount="45">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="69" uniqueCount="52">
   <si>
     <t>BTS SERVICES INFORMATIQUES AUX ORGANISATIONS</t>
   </si>
   <si>
-    <t>SESSION 2023</t>
-  </si>
-  <si>
     <t xml:space="preserve">Tableau de synthèse des réalisations professionnelles </t>
   </si>
   <si>
-    <t xml:space="preserve">N° candidat : </t>
-  </si>
-  <si>
     <t>Option :</t>
-  </si>
-  <si>
-    <t>▢ SISR</t>
   </si>
   <si>
     <t>▢ SLAM</t>
@@ -126,75 +117,104 @@
 </t>
   </si>
   <si>
-    <t>Création d'une machine virtuelle Debian ( sur Vmware)</t>
-  </si>
-  <si>
     <t>2023 - 2024</t>
   </si>
   <si>
-    <t>Etudes des protocoles de communication TCP/IP</t>
-  </si>
-  <si>
-    <t>2022 - 2023</t>
-  </si>
-  <si>
-    <t>Mise en place d'une infrastructure système et réseau sous Cisco Packet Tracer</t>
-  </si>
-  <si>
-    <t>2022 - 2024</t>
-  </si>
-  <si>
-    <t>Création d'Active Directory + Gestion des droits</t>
-  </si>
-  <si>
-    <t>Apprentissage de languages de codages (HTML,Css,PHP)</t>
-  </si>
-  <si>
-    <t>Création d'une machine virtuelle Windows 10 ( sur Vmware)_x000D_</t>
-  </si>
-  <si>
-    <t>Création d'un site avec HTML/CSS/PHP</t>
-  </si>
-  <si>
-    <t>Mise en service DHCP, DNS, Active Directory sous windows server</t>
-  </si>
-  <si>
-    <t>Adressage IP d'une infrastructure système et réseaux</t>
-  </si>
-  <si>
     <t>Réalisations en milieu professionnel en cours de première année</t>
   </si>
   <si>
-    <t>Intervention en distanciel (AnyDesk)</t>
-  </si>
-  <si>
-    <t>vérifications d'équipements informatiques, 
-logiciels et création de comptes utilisateurs</t>
-  </si>
-  <si>
-    <t>Gestion de l'inventaire de l'entreprise à Distance</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Assistance utilisateurs (matériel, logiciel, réseaux) </t>
-  </si>
-  <si>
     <t>Réalisations en milieu professionnel en cours de seconde année</t>
   </si>
   <si>
-    <t>Assistance utilisateurs (matériel, logiciel, réseaux)</t>
-  </si>
-  <si>
-    <t>vérifications d'équipements informatiques, 
-logiciels et création de comptes utilisateur</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Adresse URL du portfolio : </t>
-  </si>
-  <si>
     <t>Centre de formation : Schola Nova</t>
   </si>
   <si>
     <t>NOM et prénom : LIN Dany</t>
+  </si>
+  <si>
+    <t>Installation d'une machine virtuelle sur VMWare</t>
+  </si>
+  <si>
+    <t>Installation et configuration d'un DNS</t>
+  </si>
+  <si>
+    <t>Installation et configuration d'un DHCP</t>
+  </si>
+  <si>
+    <t>Création d'un portfolio</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mise en place d'un controleur de domaine et Installation d'un Active Directory
+</t>
+  </si>
+  <si>
+    <t>Mise en place et configuration d'un OPNsense</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Simulation d'une infrastructure réseau Cisco Packet Tracer </t>
+  </si>
+  <si>
+    <t>Mise à jour Profil Linkedin</t>
+  </si>
+  <si>
+    <t>2024 - 2026</t>
+  </si>
+  <si>
+    <t>2024 - 2025</t>
+  </si>
+  <si>
+    <t>2025-2026</t>
+  </si>
+  <si>
+    <t>Intervention en distanciel (TeamViewer)</t>
+  </si>
+  <si>
+    <t>Intégration de nouveau postes dans le domaine</t>
+  </si>
+  <si>
+    <t>Préparation et déploiement de postes de travail</t>
+  </si>
+  <si>
+    <t>Mise à jour de l'inventaire du parc informatique</t>
+  </si>
+  <si>
+    <t>Réinitialisation de mot de passe</t>
+  </si>
+  <si>
+    <t>Création de compte dans l'Active Directory</t>
+  </si>
+  <si>
+    <t>Intégration et déploiement d'application métier dans le parc informatique avec Microsoft Intune</t>
+  </si>
+  <si>
+    <t>Suivi des Tickets GLPI/Mails</t>
+  </si>
+  <si>
+    <t>Mise à jour de Procédure</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Participation au projet de sécurisation des comptes </t>
+  </si>
+  <si>
+    <t>Création de groupe de sécurité dans l'Admin Microsoft</t>
+  </si>
+  <si>
+    <t>Ajout d'un groupe de sécurité à un utilisateur</t>
+  </si>
+  <si>
+    <t>Création de compte pour les restaurants de la Franchise</t>
+  </si>
+  <si>
+    <t>X SISR</t>
+  </si>
+  <si>
+    <t>N° candidat : 02541487389</t>
+  </si>
+  <si>
+    <t>SESSION 2026</t>
+  </si>
+  <si>
+    <t>Adresse URL du portfolio : danylin-portfolio.fr</t>
   </si>
 </sst>
 </file>
@@ -280,7 +300,7 @@
       <charset val="1"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -290,12 +310,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="3" tint="0.59999389629810485"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF002060"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -697,7 +711,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="52">
+  <cellXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
@@ -729,9 +743,6 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -772,16 +783,10 @@
     <xf numFmtId="0" fontId="2" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -1158,7 +1163,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:AQ81"/>
+  <dimension ref="A1:AQ78"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="10.88671875" defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="70.44140625" style="1" customWidth="1"/>
@@ -1169,124 +1174,124 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:43" ht="39.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="30" t="s">
+      <c r="A1" s="27" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="30"/>
-      <c r="C1" s="30"/>
-      <c r="D1" s="30"/>
-      <c r="E1" s="30"/>
-      <c r="F1" s="30"/>
-      <c r="G1" s="30" t="s">
+      <c r="B1" s="27"/>
+      <c r="C1" s="27"/>
+      <c r="D1" s="27"/>
+      <c r="E1" s="27"/>
+      <c r="F1" s="27"/>
+      <c r="G1" s="27" t="s">
+        <v>50</v>
+      </c>
+      <c r="H1" s="27"/>
+    </row>
+    <row r="2" spans="1:43" ht="41.1" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="27" t="s">
         <v>1</v>
       </c>
-      <c r="H1" s="30"/>
-    </row>
-    <row r="2" spans="1:43" ht="41.1" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="30" t="s">
-        <v>2</v>
-      </c>
-      <c r="B2" s="30"/>
-      <c r="C2" s="30"/>
-      <c r="D2" s="30"/>
-      <c r="E2" s="30"/>
-      <c r="F2" s="30"/>
-      <c r="G2" s="30"/>
-      <c r="H2" s="30"/>
+      <c r="B2" s="27"/>
+      <c r="C2" s="27"/>
+      <c r="D2" s="27"/>
+      <c r="E2" s="27"/>
+      <c r="F2" s="27"/>
+      <c r="G2" s="27"/>
+      <c r="H2" s="27"/>
     </row>
     <row r="3" spans="1:43" ht="39.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="31" t="s">
-        <v>44</v>
-      </c>
-      <c r="B3" s="32"/>
-      <c r="C3" s="32"/>
-      <c r="D3" s="32"/>
-      <c r="E3" s="33"/>
-      <c r="F3" s="37" t="s">
-        <v>3</v>
-      </c>
-      <c r="G3" s="32"/>
-      <c r="H3" s="38"/>
+      <c r="A3" s="28" t="s">
+        <v>23</v>
+      </c>
+      <c r="B3" s="29"/>
+      <c r="C3" s="29"/>
+      <c r="D3" s="29"/>
+      <c r="E3" s="30"/>
+      <c r="F3" s="34" t="s">
+        <v>49</v>
+      </c>
+      <c r="G3" s="29"/>
+      <c r="H3" s="35"/>
       <c r="K3" s="1"/>
       <c r="L3" s="1"/>
       <c r="M3" s="1"/>
     </row>
     <row r="4" spans="1:43" ht="39.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="34" t="s">
-        <v>43</v>
-      </c>
-      <c r="B4" s="35"/>
-      <c r="C4" s="35"/>
-      <c r="D4" s="35"/>
-      <c r="E4" s="36"/>
-      <c r="F4" s="12" t="s">
+      <c r="A4" s="31" t="s">
+        <v>22</v>
+      </c>
+      <c r="B4" s="32"/>
+      <c r="C4" s="32"/>
+      <c r="D4" s="32"/>
+      <c r="E4" s="33"/>
+      <c r="F4" s="11" t="s">
+        <v>2</v>
+      </c>
+      <c r="G4" s="19" t="s">
+        <v>48</v>
+      </c>
+      <c r="H4" s="16" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="5" spans="1:43" ht="39.9" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A5" s="46" t="s">
+        <v>51</v>
+      </c>
+      <c r="B5" s="47"/>
+      <c r="C5" s="47"/>
+      <c r="D5" s="47"/>
+      <c r="E5" s="47"/>
+      <c r="F5" s="47"/>
+      <c r="G5" s="47"/>
+      <c r="H5" s="48"/>
+    </row>
+    <row r="6" spans="1:43" ht="90" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="36" t="s">
         <v>4</v>
       </c>
-      <c r="G4" s="20" t="s">
+      <c r="B6" s="44" t="s">
         <v>5</v>
       </c>
-      <c r="H4" s="17" t="s">
+      <c r="C6" s="6" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="5" spans="1:43" ht="39.9" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="49" t="s">
-        <v>42</v>
-      </c>
-      <c r="B5" s="50"/>
-      <c r="C5" s="50"/>
-      <c r="D5" s="50"/>
-      <c r="E5" s="50"/>
-      <c r="F5" s="50"/>
-      <c r="G5" s="50"/>
-      <c r="H5" s="51"/>
-    </row>
-    <row r="6" spans="1:43" ht="90" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="39" t="s">
+      <c r="D6" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="B6" s="47" t="s">
+      <c r="E6" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="C6" s="6" t="s">
+      <c r="F6" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="D6" s="6" t="s">
+      <c r="G6" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="E6" s="6" t="s">
+      <c r="H6" s="7" t="s">
         <v>11</v>
       </c>
-      <c r="F6" s="6" t="s">
+    </row>
+    <row r="7" spans="1:43" s="2" customFormat="1" ht="324.89999999999998" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="37"/>
+      <c r="B7" s="45"/>
+      <c r="C7" s="17" t="s">
         <v>12</v>
       </c>
-      <c r="G6" s="6" t="s">
+      <c r="D7" s="17" t="s">
         <v>13</v>
       </c>
-      <c r="H6" s="7" t="s">
+      <c r="E7" s="17" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="7" spans="1:43" s="2" customFormat="1" ht="324.89999999999998" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="40"/>
-      <c r="B7" s="48"/>
-      <c r="C7" s="18" t="s">
+      <c r="F7" s="17" t="s">
         <v>15</v>
       </c>
-      <c r="D7" s="18" t="s">
+      <c r="G7" s="17" t="s">
         <v>16</v>
       </c>
-      <c r="E7" s="18" t="s">
+      <c r="H7" s="18" t="s">
         <v>17</v>
-      </c>
-      <c r="F7" s="18" t="s">
-        <v>18</v>
-      </c>
-      <c r="G7" s="18" t="s">
-        <v>19</v>
-      </c>
-      <c r="H7" s="19" t="s">
-        <v>20</v>
       </c>
       <c r="I7"/>
       <c r="J7"/>
@@ -1325,16 +1330,16 @@
       <c r="AQ7"/>
     </row>
     <row r="8" spans="1:43" s="2" customFormat="1" ht="17.399999999999999" x14ac:dyDescent="0.25">
-      <c r="A8" s="41" t="s">
-        <v>21</v>
-      </c>
-      <c r="B8" s="42"/>
-      <c r="C8" s="42"/>
-      <c r="D8" s="42"/>
-      <c r="E8" s="42"/>
-      <c r="F8" s="42"/>
-      <c r="G8" s="42"/>
-      <c r="H8" s="43"/>
+      <c r="A8" s="38" t="s">
+        <v>18</v>
+      </c>
+      <c r="B8" s="39"/>
+      <c r="C8" s="39"/>
+      <c r="D8" s="39"/>
+      <c r="E8" s="39"/>
+      <c r="F8" s="39"/>
+      <c r="G8" s="39"/>
+      <c r="H8" s="40"/>
       <c r="I8"/>
       <c r="J8"/>
       <c r="K8"/>
@@ -1373,17 +1378,17 @@
     </row>
     <row r="9" spans="1:43" s="2" customFormat="1" ht="39.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="9" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="B9" s="8" t="s">
-        <v>23</v>
-      </c>
-      <c r="C9" s="22"/>
-      <c r="D9" s="23"/>
-      <c r="E9" s="13"/>
-      <c r="F9" s="23"/>
-      <c r="G9" s="24"/>
-      <c r="H9" s="13"/>
+        <v>32</v>
+      </c>
+      <c r="C9" s="21"/>
+      <c r="D9" s="22"/>
+      <c r="E9" s="12"/>
+      <c r="F9" s="12"/>
+      <c r="G9" s="23"/>
+      <c r="H9" s="12"/>
       <c r="I9"/>
       <c r="J9"/>
       <c r="K9"/>
@@ -1422,17 +1427,17 @@
     </row>
     <row r="10" spans="1:43" s="2" customFormat="1" ht="39.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="9" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B10" s="8" t="s">
-        <v>25</v>
-      </c>
-      <c r="C10" s="23"/>
-      <c r="D10" s="13"/>
-      <c r="E10" s="23"/>
-      <c r="F10" s="13"/>
-      <c r="G10" s="13"/>
-      <c r="H10" s="25"/>
+        <v>33</v>
+      </c>
+      <c r="C10" s="22"/>
+      <c r="D10" s="22"/>
+      <c r="E10" s="12"/>
+      <c r="F10" s="12"/>
+      <c r="G10" s="22"/>
+      <c r="H10" s="12"/>
       <c r="I10"/>
       <c r="J10"/>
       <c r="K10"/>
@@ -1474,14 +1479,14 @@
         <v>26</v>
       </c>
       <c r="B11" s="8" t="s">
-        <v>27</v>
-      </c>
-      <c r="C11" s="23"/>
-      <c r="D11" s="23"/>
-      <c r="E11" s="13"/>
-      <c r="F11" s="23"/>
-      <c r="G11" s="23"/>
-      <c r="H11" s="14"/>
+        <v>33</v>
+      </c>
+      <c r="C11" s="22"/>
+      <c r="D11" s="22"/>
+      <c r="E11" s="12"/>
+      <c r="F11" s="12"/>
+      <c r="G11" s="22"/>
+      <c r="H11" s="13"/>
       <c r="I11"/>
       <c r="J11"/>
       <c r="K11"/>
@@ -1520,17 +1525,17 @@
     </row>
     <row r="12" spans="1:43" s="2" customFormat="1" ht="39.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="9" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B12" s="8" t="s">
-        <v>23</v>
-      </c>
-      <c r="C12" s="13"/>
-      <c r="D12" s="13"/>
-      <c r="E12" s="23"/>
-      <c r="F12" s="13"/>
-      <c r="G12" s="13"/>
-      <c r="H12" s="25"/>
+        <v>34</v>
+      </c>
+      <c r="C12" s="22"/>
+      <c r="D12" s="22"/>
+      <c r="E12" s="12"/>
+      <c r="F12" s="12"/>
+      <c r="G12" s="22"/>
+      <c r="H12" s="12"/>
       <c r="I12"/>
       <c r="J12"/>
       <c r="K12"/>
@@ -1569,17 +1574,17 @@
     </row>
     <row r="13" spans="1:43" s="2" customFormat="1" ht="39.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="9" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="B13" s="8" t="s">
-        <v>25</v>
-      </c>
-      <c r="C13" s="23"/>
-      <c r="D13" s="23"/>
-      <c r="E13" s="23"/>
-      <c r="F13" s="13"/>
-      <c r="G13" s="23"/>
-      <c r="H13" s="14"/>
+        <v>32</v>
+      </c>
+      <c r="C13" s="22"/>
+      <c r="D13" s="12"/>
+      <c r="E13" s="22"/>
+      <c r="F13" s="12"/>
+      <c r="G13" s="12"/>
+      <c r="H13" s="13"/>
       <c r="I13"/>
       <c r="J13"/>
       <c r="K13"/>
@@ -1618,17 +1623,17 @@
     </row>
     <row r="14" spans="1:43" s="2" customFormat="1" ht="39.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="9" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="B14" s="8" t="s">
-        <v>25</v>
-      </c>
-      <c r="C14" s="23"/>
-      <c r="D14" s="23"/>
-      <c r="E14" s="13"/>
-      <c r="F14" s="23"/>
-      <c r="G14" s="13"/>
-      <c r="H14" s="25"/>
+        <v>32</v>
+      </c>
+      <c r="C14" s="22"/>
+      <c r="D14" s="22"/>
+      <c r="E14" s="12"/>
+      <c r="F14" s="22"/>
+      <c r="G14" s="24"/>
+      <c r="H14" s="12"/>
       <c r="I14"/>
       <c r="J14"/>
       <c r="K14"/>
@@ -1667,17 +1672,17 @@
     </row>
     <row r="15" spans="1:43" s="2" customFormat="1" ht="39.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="9" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B15" s="8" t="s">
-        <v>25</v>
-      </c>
-      <c r="C15" s="23"/>
-      <c r="D15" s="13"/>
-      <c r="E15" s="23"/>
-      <c r="F15" s="23"/>
-      <c r="G15" s="23"/>
-      <c r="H15" s="25"/>
+        <v>32</v>
+      </c>
+      <c r="C15" s="22"/>
+      <c r="D15" s="22"/>
+      <c r="E15" s="12"/>
+      <c r="F15" s="12"/>
+      <c r="G15" s="22"/>
+      <c r="H15" s="12"/>
       <c r="I15"/>
       <c r="J15"/>
       <c r="K15"/>
@@ -1715,18 +1720,18 @@
       <c r="AQ15"/>
     </row>
     <row r="16" spans="1:43" s="2" customFormat="1" ht="39.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="28" t="s">
+      <c r="A16" s="25" t="s">
+        <v>31</v>
+      </c>
+      <c r="B16" s="8" t="s">
         <v>32</v>
       </c>
-      <c r="B16" s="8" t="s">
-        <v>23</v>
-      </c>
-      <c r="C16" s="23"/>
-      <c r="D16" s="23"/>
-      <c r="E16" s="13"/>
-      <c r="F16" s="13"/>
-      <c r="G16" s="23"/>
-      <c r="H16" s="14"/>
+      <c r="C16" s="12"/>
+      <c r="D16" s="12"/>
+      <c r="E16" s="12"/>
+      <c r="F16" s="12"/>
+      <c r="G16" s="12"/>
+      <c r="H16" s="22"/>
       <c r="I16"/>
       <c r="J16"/>
       <c r="K16"/>
@@ -1763,19 +1768,17 @@
       <c r="AP16"/>
       <c r="AQ16"/>
     </row>
-    <row r="17" spans="1:43" s="2" customFormat="1" ht="39.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="9" t="s">
-        <v>33</v>
-      </c>
-      <c r="B17" s="8" t="s">
-        <v>23</v>
-      </c>
-      <c r="C17" s="23"/>
-      <c r="D17" s="23"/>
-      <c r="E17" s="23"/>
-      <c r="F17" s="13"/>
-      <c r="G17" s="23"/>
-      <c r="H17" s="25"/>
+    <row r="17" spans="1:43" s="2" customFormat="1" ht="17.399999999999999" x14ac:dyDescent="0.25">
+      <c r="A17" s="41" t="s">
+        <v>20</v>
+      </c>
+      <c r="B17" s="42"/>
+      <c r="C17" s="42"/>
+      <c r="D17" s="42"/>
+      <c r="E17" s="42"/>
+      <c r="F17" s="42"/>
+      <c r="G17" s="42"/>
+      <c r="H17" s="43"/>
       <c r="I17"/>
       <c r="J17"/>
       <c r="K17"/>
@@ -1813,14 +1816,18 @@
       <c r="AQ17"/>
     </row>
     <row r="18" spans="1:43" s="2" customFormat="1" ht="39.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="9"/>
-      <c r="B18" s="8"/>
-      <c r="C18" s="13"/>
-      <c r="D18" s="13"/>
-      <c r="E18" s="13"/>
+      <c r="A18" s="9" t="s">
+        <v>35</v>
+      </c>
+      <c r="B18" s="8" t="s">
+        <v>32</v>
+      </c>
+      <c r="C18" s="26"/>
+      <c r="D18" s="22"/>
+      <c r="E18" s="26"/>
       <c r="F18" s="13"/>
-      <c r="G18" s="13"/>
-      <c r="H18" s="14"/>
+      <c r="G18" s="22"/>
+      <c r="H18" s="13"/>
       <c r="I18"/>
       <c r="J18"/>
       <c r="K18"/>
@@ -1857,17 +1864,19 @@
       <c r="AP18"/>
       <c r="AQ18"/>
     </row>
-    <row r="19" spans="1:43" s="2" customFormat="1" ht="17.399999999999999" x14ac:dyDescent="0.25">
-      <c r="A19" s="44" t="s">
-        <v>34</v>
-      </c>
-      <c r="B19" s="45"/>
-      <c r="C19" s="45"/>
-      <c r="D19" s="45"/>
-      <c r="E19" s="45"/>
-      <c r="F19" s="45"/>
-      <c r="G19" s="45"/>
-      <c r="H19" s="46"/>
+    <row r="19" spans="1:43" s="2" customFormat="1" ht="39.9" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A19" s="9" t="s">
+        <v>37</v>
+      </c>
+      <c r="B19" s="8" t="s">
+        <v>32</v>
+      </c>
+      <c r="C19" s="22"/>
+      <c r="D19" s="22"/>
+      <c r="E19" s="13"/>
+      <c r="F19" s="13"/>
+      <c r="G19" s="22"/>
+      <c r="H19" s="13"/>
       <c r="I19"/>
       <c r="J19"/>
       <c r="K19"/>
@@ -1906,17 +1915,17 @@
     </row>
     <row r="20" spans="1:43" s="2" customFormat="1" ht="39.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="9" t="s">
-        <v>35</v>
-      </c>
-      <c r="B20" s="8" t="s">
-        <v>25</v>
-      </c>
-      <c r="C20" s="26"/>
-      <c r="D20" s="26"/>
-      <c r="E20" s="29"/>
-      <c r="F20" s="26"/>
-      <c r="G20" s="26"/>
-      <c r="H20" s="14"/>
+        <v>36</v>
+      </c>
+      <c r="B20" s="20" t="s">
+        <v>32</v>
+      </c>
+      <c r="C20" s="22"/>
+      <c r="D20" s="13"/>
+      <c r="E20" s="13"/>
+      <c r="F20" s="12"/>
+      <c r="G20" s="22"/>
+      <c r="H20" s="12"/>
       <c r="I20"/>
       <c r="J20"/>
       <c r="K20"/>
@@ -1955,17 +1964,17 @@
     </row>
     <row r="21" spans="1:43" s="2" customFormat="1" ht="39.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="9" t="s">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="B21" s="8" t="s">
-        <v>25</v>
-      </c>
-      <c r="C21" s="26"/>
-      <c r="D21" s="26"/>
+        <v>32</v>
+      </c>
+      <c r="C21" s="12"/>
+      <c r="D21" s="22"/>
       <c r="E21" s="26"/>
-      <c r="F21" s="26"/>
-      <c r="G21" s="13"/>
-      <c r="H21" s="27"/>
+      <c r="F21" s="12"/>
+      <c r="G21" s="22"/>
+      <c r="H21" s="13"/>
       <c r="I21"/>
       <c r="J21"/>
       <c r="K21"/>
@@ -2004,17 +2013,17 @@
     </row>
     <row r="22" spans="1:43" s="2" customFormat="1" ht="39.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="9" t="s">
-        <v>37</v>
-      </c>
-      <c r="B22" s="21" t="s">
-        <v>25</v>
-      </c>
-      <c r="C22" s="26"/>
-      <c r="D22" s="26"/>
-      <c r="E22" s="26"/>
-      <c r="F22" s="13"/>
-      <c r="G22" s="13"/>
-      <c r="H22" s="27"/>
+        <v>40</v>
+      </c>
+      <c r="B22" s="8" t="s">
+        <v>32</v>
+      </c>
+      <c r="C22" s="22"/>
+      <c r="D22" s="12"/>
+      <c r="E22" s="12"/>
+      <c r="F22" s="12"/>
+      <c r="G22" s="22"/>
+      <c r="H22" s="13"/>
       <c r="I22"/>
       <c r="J22"/>
       <c r="K22"/>
@@ -2056,14 +2065,14 @@
         <v>38</v>
       </c>
       <c r="B23" s="8" t="s">
-        <v>25</v>
-      </c>
-      <c r="C23" s="26"/>
-      <c r="D23" s="26"/>
-      <c r="E23" s="29"/>
-      <c r="F23" s="26"/>
-      <c r="G23" s="26"/>
-      <c r="H23" s="14"/>
+        <v>32</v>
+      </c>
+      <c r="C23" s="22"/>
+      <c r="D23" s="12"/>
+      <c r="E23" s="12"/>
+      <c r="F23" s="12"/>
+      <c r="G23" s="12"/>
+      <c r="H23" s="13"/>
       <c r="I23"/>
       <c r="J23"/>
       <c r="K23"/>
@@ -2101,14 +2110,18 @@
       <c r="AQ23"/>
     </row>
     <row r="24" spans="1:43" s="2" customFormat="1" ht="39.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="9"/>
-      <c r="B24" s="8"/>
-      <c r="C24" s="13"/>
-      <c r="D24" s="13"/>
-      <c r="E24" s="13"/>
-      <c r="F24" s="13"/>
-      <c r="G24" s="13"/>
-      <c r="H24" s="14"/>
+      <c r="A24" s="9" t="s">
+        <v>39</v>
+      </c>
+      <c r="B24" s="8" t="s">
+        <v>32</v>
+      </c>
+      <c r="C24" s="12"/>
+      <c r="D24" s="22"/>
+      <c r="E24" s="12"/>
+      <c r="F24" s="12"/>
+      <c r="G24" s="22"/>
+      <c r="H24" s="13"/>
       <c r="I24"/>
       <c r="J24"/>
       <c r="K24"/>
@@ -2145,15 +2158,17 @@
       <c r="AP24"/>
       <c r="AQ24"/>
     </row>
-    <row r="25" spans="1:43" s="2" customFormat="1" ht="39.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A25" s="9"/>
-      <c r="B25" s="8"/>
-      <c r="C25" s="13"/>
-      <c r="D25" s="13"/>
-      <c r="E25" s="13"/>
-      <c r="F25" s="13"/>
-      <c r="G25" s="13"/>
-      <c r="H25" s="14"/>
+    <row r="25" spans="1:43" s="2" customFormat="1" ht="17.399999999999999" x14ac:dyDescent="0.25">
+      <c r="A25" s="41" t="s">
+        <v>21</v>
+      </c>
+      <c r="B25" s="42"/>
+      <c r="C25" s="42"/>
+      <c r="D25" s="42"/>
+      <c r="E25" s="42"/>
+      <c r="F25" s="42"/>
+      <c r="G25" s="42"/>
+      <c r="H25" s="43"/>
       <c r="I25"/>
       <c r="J25"/>
       <c r="K25"/>
@@ -2191,14 +2206,18 @@
       <c r="AQ25"/>
     </row>
     <row r="26" spans="1:43" s="2" customFormat="1" ht="39.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="9"/>
-      <c r="B26" s="8"/>
-      <c r="C26" s="13"/>
-      <c r="D26" s="13"/>
-      <c r="E26" s="13"/>
-      <c r="F26" s="13"/>
-      <c r="G26" s="13"/>
-      <c r="H26" s="14"/>
+      <c r="A26" s="9" t="s">
+        <v>41</v>
+      </c>
+      <c r="B26" s="8" t="s">
+        <v>32</v>
+      </c>
+      <c r="C26" s="22"/>
+      <c r="D26" s="22"/>
+      <c r="E26" s="26"/>
+      <c r="F26" s="22"/>
+      <c r="G26" s="22"/>
+      <c r="H26" s="13"/>
       <c r="I26"/>
       <c r="J26"/>
       <c r="K26"/>
@@ -2235,17 +2254,19 @@
       <c r="AP26"/>
       <c r="AQ26"/>
     </row>
-    <row r="27" spans="1:43" s="2" customFormat="1" ht="17.399999999999999" x14ac:dyDescent="0.25">
-      <c r="A27" s="44" t="s">
-        <v>39</v>
-      </c>
-      <c r="B27" s="45"/>
-      <c r="C27" s="45"/>
-      <c r="D27" s="45"/>
-      <c r="E27" s="45"/>
-      <c r="F27" s="45"/>
-      <c r="G27" s="45"/>
-      <c r="H27" s="46"/>
+    <row r="27" spans="1:43" s="2" customFormat="1" ht="39.9" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A27" s="9" t="s">
+        <v>44</v>
+      </c>
+      <c r="B27" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="C27" s="22"/>
+      <c r="D27" s="13"/>
+      <c r="E27" s="13"/>
+      <c r="F27" s="22"/>
+      <c r="G27" s="22"/>
+      <c r="H27" s="13"/>
       <c r="I27"/>
       <c r="J27"/>
       <c r="K27"/>
@@ -2284,17 +2305,17 @@
     </row>
     <row r="28" spans="1:43" s="2" customFormat="1" ht="39.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="9" t="s">
-        <v>40</v>
+        <v>47</v>
       </c>
       <c r="B28" s="8" t="s">
-        <v>23</v>
-      </c>
-      <c r="C28" s="26"/>
-      <c r="D28" s="26"/>
-      <c r="E28" s="29"/>
-      <c r="F28" s="26"/>
-      <c r="G28" s="26"/>
-      <c r="H28" s="14"/>
+        <v>32</v>
+      </c>
+      <c r="C28" s="22"/>
+      <c r="D28" s="13"/>
+      <c r="E28" s="13"/>
+      <c r="F28" s="13"/>
+      <c r="G28" s="22"/>
+      <c r="H28" s="13"/>
       <c r="I28"/>
       <c r="J28"/>
       <c r="K28"/>
@@ -2333,17 +2354,17 @@
     </row>
     <row r="29" spans="1:43" s="2" customFormat="1" ht="39.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="9" t="s">
-        <v>35</v>
+        <v>43</v>
       </c>
       <c r="B29" s="8" t="s">
-        <v>23</v>
-      </c>
-      <c r="C29" s="26"/>
-      <c r="D29" s="26"/>
-      <c r="E29" s="26"/>
-      <c r="F29" s="26"/>
-      <c r="G29" s="13"/>
-      <c r="H29" s="27"/>
+        <v>32</v>
+      </c>
+      <c r="C29" s="12"/>
+      <c r="D29" s="12"/>
+      <c r="E29" s="22"/>
+      <c r="F29" s="12"/>
+      <c r="G29" s="12"/>
+      <c r="H29" s="22"/>
       <c r="I29"/>
       <c r="J29"/>
       <c r="K29"/>
@@ -2382,17 +2403,17 @@
     </row>
     <row r="30" spans="1:43" s="2" customFormat="1" ht="39.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="9" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="B30" s="8" t="s">
-        <v>23</v>
-      </c>
-      <c r="C30" s="26"/>
-      <c r="D30" s="26"/>
-      <c r="E30" s="26"/>
-      <c r="F30" s="13"/>
-      <c r="G30" s="13"/>
-      <c r="H30" s="27"/>
+        <v>32</v>
+      </c>
+      <c r="C30" s="12"/>
+      <c r="D30" s="22"/>
+      <c r="E30" s="12"/>
+      <c r="F30" s="12"/>
+      <c r="G30" s="22"/>
+      <c r="H30" s="13"/>
       <c r="I30"/>
       <c r="J30"/>
       <c r="K30"/>
@@ -2429,19 +2450,19 @@
       <c r="AP30"/>
       <c r="AQ30"/>
     </row>
-    <row r="31" spans="1:43" s="2" customFormat="1" ht="39.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A31" s="9" t="s">
-        <v>37</v>
+    <row r="31" spans="1:43" s="2" customFormat="1" ht="39.9" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A31" s="10" t="s">
+        <v>46</v>
       </c>
       <c r="B31" s="8" t="s">
-        <v>23</v>
-      </c>
-      <c r="C31" s="26"/>
-      <c r="D31" s="26"/>
-      <c r="E31" s="26"/>
-      <c r="F31" s="26"/>
-      <c r="G31" s="26"/>
-      <c r="H31" s="14"/>
+        <v>32</v>
+      </c>
+      <c r="C31" s="22"/>
+      <c r="D31" s="14"/>
+      <c r="E31" s="14"/>
+      <c r="F31" s="14"/>
+      <c r="G31" s="22"/>
+      <c r="H31" s="15"/>
       <c r="I31"/>
       <c r="J31"/>
       <c r="K31"/>
@@ -2478,15 +2499,15 @@
       <c r="AP31"/>
       <c r="AQ31"/>
     </row>
-    <row r="32" spans="1:43" s="2" customFormat="1" ht="39.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A32" s="9"/>
-      <c r="B32" s="8"/>
-      <c r="C32" s="13"/>
-      <c r="D32" s="13"/>
-      <c r="E32" s="13"/>
-      <c r="F32" s="13"/>
-      <c r="G32" s="13"/>
-      <c r="H32" s="14"/>
+    <row r="32" spans="1:43" s="2" customFormat="1" ht="13.8" x14ac:dyDescent="0.25">
+      <c r="A32" s="5"/>
+      <c r="B32" s="3"/>
+      <c r="C32" s="4"/>
+      <c r="D32" s="4"/>
+      <c r="E32" s="4"/>
+      <c r="F32" s="4"/>
+      <c r="G32" s="4"/>
+      <c r="H32" s="4"/>
       <c r="I32"/>
       <c r="J32"/>
       <c r="K32"/>
@@ -2523,154 +2544,22 @@
       <c r="AP32"/>
       <c r="AQ32"/>
     </row>
-    <row r="33" spans="1:43" s="2" customFormat="1" ht="39.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A33" s="9"/>
-      <c r="B33" s="8"/>
-      <c r="C33" s="13"/>
-      <c r="D33" s="13"/>
-      <c r="E33" s="13"/>
-      <c r="F33" s="13"/>
-      <c r="G33" s="13"/>
-      <c r="H33" s="14"/>
-      <c r="I33"/>
-      <c r="J33"/>
-      <c r="K33"/>
-      <c r="L33"/>
-      <c r="M33"/>
-      <c r="N33"/>
-      <c r="O33"/>
-      <c r="P33"/>
-      <c r="Q33"/>
-      <c r="R33"/>
-      <c r="S33"/>
-      <c r="T33"/>
-      <c r="U33"/>
-      <c r="V33"/>
-      <c r="W33"/>
-      <c r="X33"/>
-      <c r="Y33"/>
-      <c r="Z33"/>
-      <c r="AA33"/>
-      <c r="AB33"/>
-      <c r="AC33"/>
-      <c r="AD33"/>
-      <c r="AE33"/>
-      <c r="AF33"/>
-      <c r="AG33"/>
-      <c r="AH33"/>
-      <c r="AI33"/>
-      <c r="AJ33"/>
-      <c r="AK33"/>
-      <c r="AL33"/>
-      <c r="AM33"/>
-      <c r="AN33"/>
-      <c r="AO33"/>
-      <c r="AP33"/>
-      <c r="AQ33"/>
-    </row>
-    <row r="34" spans="1:43" s="2" customFormat="1" ht="39.9" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A34" s="10"/>
-      <c r="B34" s="11"/>
-      <c r="C34" s="15"/>
-      <c r="D34" s="15"/>
-      <c r="E34" s="15"/>
-      <c r="F34" s="15"/>
-      <c r="G34" s="15"/>
-      <c r="H34" s="16"/>
-      <c r="I34"/>
-      <c r="J34"/>
-      <c r="K34"/>
-      <c r="L34"/>
-      <c r="M34"/>
-      <c r="N34"/>
-      <c r="O34"/>
-      <c r="P34"/>
-      <c r="Q34"/>
-      <c r="R34"/>
-      <c r="S34"/>
-      <c r="T34"/>
-      <c r="U34"/>
-      <c r="V34"/>
-      <c r="W34"/>
-      <c r="X34"/>
-      <c r="Y34"/>
-      <c r="Z34"/>
-      <c r="AA34"/>
-      <c r="AB34"/>
-      <c r="AC34"/>
-      <c r="AD34"/>
-      <c r="AE34"/>
-      <c r="AF34"/>
-      <c r="AG34"/>
-      <c r="AH34"/>
-      <c r="AI34"/>
-      <c r="AJ34"/>
-      <c r="AK34"/>
-      <c r="AL34"/>
-      <c r="AM34"/>
-      <c r="AN34"/>
-      <c r="AO34"/>
-      <c r="AP34"/>
-      <c r="AQ34"/>
-    </row>
-    <row r="35" spans="1:43" s="2" customFormat="1" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A35" s="5"/>
-      <c r="B35" s="3"/>
-      <c r="C35" s="4"/>
-      <c r="D35" s="4"/>
-      <c r="E35" s="4"/>
-      <c r="F35" s="4"/>
-      <c r="G35" s="4"/>
-      <c r="H35" s="4"/>
-      <c r="I35"/>
-      <c r="J35"/>
-      <c r="K35"/>
-      <c r="L35"/>
-      <c r="M35"/>
-      <c r="N35"/>
-      <c r="O35"/>
-      <c r="P35"/>
-      <c r="Q35"/>
-      <c r="R35"/>
-      <c r="S35"/>
-      <c r="T35"/>
-      <c r="U35"/>
-      <c r="V35"/>
-      <c r="W35"/>
-      <c r="X35"/>
-      <c r="Y35"/>
-      <c r="Z35"/>
-      <c r="AA35"/>
-      <c r="AB35"/>
-      <c r="AC35"/>
-      <c r="AD35"/>
-      <c r="AE35"/>
-      <c r="AF35"/>
-      <c r="AG35"/>
-      <c r="AH35"/>
-      <c r="AI35"/>
-      <c r="AJ35"/>
-      <c r="AK35"/>
-      <c r="AL35"/>
-      <c r="AM35"/>
-      <c r="AN35"/>
-      <c r="AO35"/>
-      <c r="AP35"/>
-      <c r="AQ35"/>
-    </row>
-    <row r="36" spans="1:43" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="37" spans="1:43" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="38" spans="1:43" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="39" spans="1:43" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="40" spans="1:43" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="41" spans="1:43" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="42" spans="1:43" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="43" spans="1:43" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="44" spans="1:43" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="45" spans="1:43" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="46" spans="1:43" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="47" spans="1:43" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="48" spans="1:43" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="33" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="34" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="35" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="36" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="37" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="38" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="39" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="40" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="41" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="42" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="43" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="44" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="45" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="46" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="47" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="48" customFormat="1" x14ac:dyDescent="0.25"/>
     <row r="49" customFormat="1" x14ac:dyDescent="0.25"/>
     <row r="50" customFormat="1" x14ac:dyDescent="0.25"/>
     <row r="51" customFormat="1" x14ac:dyDescent="0.25"/>
@@ -2701,16 +2590,13 @@
     <row r="76" customFormat="1" x14ac:dyDescent="0.25"/>
     <row r="77" customFormat="1" x14ac:dyDescent="0.25"/>
     <row r="78" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="79" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="80" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="81" customFormat="1" x14ac:dyDescent="0.25"/>
   </sheetData>
   <mergeCells count="12">
     <mergeCell ref="A6:A7"/>
     <mergeCell ref="A2:H2"/>
     <mergeCell ref="A8:H8"/>
-    <mergeCell ref="A19:H19"/>
-    <mergeCell ref="A27:H27"/>
+    <mergeCell ref="A17:H17"/>
+    <mergeCell ref="A25:H25"/>
     <mergeCell ref="B6:B7"/>
     <mergeCell ref="A5:H5"/>
     <mergeCell ref="G1:H1"/>
